--- a/New_CenterOfRotation/Finite_COR/Data Files/C34_Data/Y_Z Data Model 2-C34.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C34_Data/Y_Z Data Model 2-C34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="17">
   <si>
     <t>Descriptions are [X,Y,Z] coords in the model. If a node is in the middle on the right, and top of C4, it would be [1,0,1] C4. Bottom would be [1,0,-1] C4</t>
   </si>
@@ -63,6 +63,9 @@
     <t>Z (U3)</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>U1, U2, U3 are displacements</t>
   </si>
   <si>
@@ -74,7 +77,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +88,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -122,6 +131,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFc6c6c6"/>
       </left>
@@ -136,62 +152,55 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -201,12 +210,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -517,100 +532,100 @@
     <col min="1" max="1" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="1"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="1"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="4"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="1"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
       <c r="U1" s="2"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="1"/>
+      <c r="L2" s="4"/>
       <c r="M2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="O2" s="6"/>
-      <c r="P2" s="1"/>
+      <c r="P2" s="4"/>
       <c r="Q2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="6"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="4"/>
       <c r="U2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>6</v>
@@ -971,7 +986,7 @@
         <v>-1.06969</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="14">
         <v>0.15</v>
       </c>
@@ -1008,7 +1023,7 @@
       <c r="N9" s="14">
         <v>1.87258</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="22">
         <v>-0.271604</v>
       </c>
       <c r="P9" s="11"/>
@@ -2085,23 +2100,23 @@
     <col min="1" max="1" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -2111,74 +2126,74 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="1"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="1"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="4"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="1"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
       <c r="U1" s="2"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="1"/>
+      <c r="L2" s="4"/>
       <c r="M2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="O2" s="6"/>
-      <c r="P2" s="1"/>
+      <c r="P2" s="4"/>
       <c r="Q2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="6"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="4"/>
       <c r="U2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V2" s="6" t="s">
         <v>6</v>
@@ -2393,7 +2408,7 @@
       <c r="N6" s="14">
         <v>1.8842</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="22">
         <v>-0.300323</v>
       </c>
       <c r="P6" s="11"/>
@@ -2454,7 +2469,7 @@
       <c r="N7" s="14">
         <v>1.76068</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="22">
         <v>-0.457465</v>
       </c>
       <c r="P7" s="11"/>
@@ -2515,7 +2530,7 @@
       <c r="N8" s="14">
         <v>1.53459</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="22">
         <v>-0.591752</v>
       </c>
       <c r="P8" s="11"/>
@@ -2576,7 +2591,7 @@
       <c r="N9" s="14">
         <v>1.30089</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="22">
         <v>-0.708137</v>
       </c>
       <c r="P9" s="11"/>
@@ -2637,7 +2652,7 @@
       <c r="N10" s="14">
         <v>0.984139</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O10" s="22">
         <v>-0.839529</v>
       </c>
       <c r="P10" s="11"/>
@@ -2698,7 +2713,7 @@
       <c r="N11" s="14">
         <v>0.711561</v>
       </c>
-      <c r="O11" s="20">
+      <c r="O11" s="22">
         <v>-0.941048</v>
       </c>
       <c r="P11" s="11"/>
@@ -2759,7 +2774,7 @@
       <c r="N12" s="14">
         <v>0.352287</v>
       </c>
-      <c r="O12" s="20">
+      <c r="O12" s="22">
         <v>-1.07039</v>
       </c>
       <c r="P12" s="11"/>
@@ -2820,7 +2835,7 @@
       <c r="N13" s="14">
         <v>-0.040455</v>
       </c>
-      <c r="O13" s="20">
+      <c r="O13" s="22">
         <v>-1.20603</v>
       </c>
       <c r="P13" s="11"/>
@@ -2881,7 +2896,7 @@
       <c r="N14" s="14">
         <v>-0.542556</v>
       </c>
-      <c r="O14" s="20">
+      <c r="O14" s="22">
         <v>-1.37859</v>
       </c>
       <c r="P14" s="11"/>
@@ -2942,7 +2957,7 @@
       <c r="N15" s="14">
         <v>-0.936973</v>
       </c>
-      <c r="O15" s="20">
+      <c r="O15" s="22">
         <v>-1.5125</v>
       </c>
       <c r="P15" s="11"/>
@@ -3003,7 +3018,7 @@
       <c r="N16" s="14">
         <v>-1.52405</v>
       </c>
-      <c r="O16" s="20">
+      <c r="O16" s="22">
         <v>-1.71496</v>
       </c>
       <c r="P16" s="11"/>
@@ -3064,7 +3079,7 @@
       <c r="N17" s="14">
         <v>-1.97305</v>
       </c>
-      <c r="O17" s="20">
+      <c r="O17" s="22">
         <v>-1.87324</v>
       </c>
       <c r="P17" s="11"/>
@@ -3125,7 +3140,7 @@
       <c r="N18" s="14">
         <v>-2.31226</v>
       </c>
-      <c r="O18" s="20">
+      <c r="O18" s="22">
         <v>-1.99645</v>
       </c>
       <c r="P18" s="11"/>
@@ -3186,7 +3201,7 @@
       <c r="N19" s="14">
         <v>-2.86265</v>
       </c>
-      <c r="O19" s="20">
+      <c r="O19" s="22">
         <v>-2.20956</v>
       </c>
       <c r="P19" s="11"/>
@@ -3247,7 +3262,7 @@
       <c r="N20" s="14">
         <v>-3.48104</v>
       </c>
-      <c r="O20" s="20">
+      <c r="O20" s="22">
         <v>-2.4731</v>
       </c>
       <c r="P20" s="11"/>
@@ -3308,7 +3323,7 @@
       <c r="N21" s="14">
         <v>-4.02582</v>
       </c>
-      <c r="O21" s="20">
+      <c r="O21" s="22">
         <v>-2.71762</v>
       </c>
       <c r="P21" s="11"/>
@@ -3369,7 +3384,7 @@
       <c r="N22" s="14">
         <v>-4.68353</v>
       </c>
-      <c r="O22" s="20">
+      <c r="O22" s="22">
         <v>-3.02456</v>
       </c>
       <c r="P22" s="11"/>
@@ -3430,7 +3445,7 @@
       <c r="N23" s="14">
         <v>-5.06963</v>
       </c>
-      <c r="O23" s="20">
+      <c r="O23" s="22">
         <v>-3.21021</v>
       </c>
       <c r="P23" s="11"/>
@@ -3491,7 +3506,7 @@
       <c r="N24" s="14">
         <v>-5.67863</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="22">
         <v>-3.51186</v>
       </c>
       <c r="P24" s="11"/>
@@ -3552,7 +3567,7 @@
       <c r="N25" s="14">
         <v>-6.29356</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25" s="22">
         <v>-3.82803</v>
       </c>
       <c r="P25" s="11"/>
@@ -3613,7 +3628,7 @@
       <c r="N26" s="14">
         <v>-6.68151</v>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="22">
         <v>-4.03325</v>
       </c>
       <c r="P26" s="11"/>
@@ -3654,27 +3669,27 @@
     <col min="2" max="2" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3686,33 +3701,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="1"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="1"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="1"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="1"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="3"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="5"/>
@@ -3721,35 +3736,35 @@
         <v>1</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="N2" s="6"/>
-      <c r="O2" s="1"/>
+      <c r="O2" s="4"/>
       <c r="P2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="4"/>
       <c r="U2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="5" t="s">
         <v>6</v>
       </c>
@@ -3758,8 +3773,8 @@
       <c r="AC2" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
+      <c r="A3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9">
@@ -3767,8 +3782,8 @@
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="7" t="s">
-        <v>7</v>
+      <c r="F3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9">
@@ -3776,8 +3791,8 @@
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="7" t="s">
-        <v>7</v>
+      <c r="K3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="9">
@@ -3785,8 +3800,8 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="7" t="s">
-        <v>7</v>
+      <c r="P3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="9">
@@ -3794,8 +3809,8 @@
       </c>
       <c r="S3" s="10"/>
       <c r="T3" s="11"/>
-      <c r="U3" s="7" t="s">
-        <v>8</v>
+      <c r="U3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="V3" s="8"/>
       <c r="W3" s="9">
@@ -3803,8 +3818,8 @@
       </c>
       <c r="X3" s="10"/>
       <c r="Y3" s="11"/>
-      <c r="Z3" s="7" t="s">
-        <v>7</v>
+      <c r="Z3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="AA3" s="8"/>
       <c r="AB3" s="9">
@@ -5394,27 +5409,27 @@
     <col min="2" max="2" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -5426,33 +5441,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="1"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="1"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="1"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="1"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="3"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="5"/>
@@ -5461,35 +5476,35 @@
         <v>1</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="N2" s="6"/>
-      <c r="O2" s="1"/>
+      <c r="O2" s="4"/>
       <c r="P2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="4"/>
       <c r="U2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="5" t="s">
         <v>6</v>
       </c>
@@ -7135,27 +7150,27 @@
     <col min="3" max="3" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="29" max="29" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -7168,33 +7183,33 @@
         <v>0</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="2"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="1"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="1"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="4"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="1"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="4"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="1"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="4"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="3"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
@@ -7204,35 +7219,35 @@
         <v>1</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2" s="1"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="O2" s="6"/>
-      <c r="P2" s="1"/>
+      <c r="P2" s="4"/>
       <c r="Q2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="U2" s="1"/>
+      <c r="U2" s="4"/>
       <c r="V2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
-      <c r="Z2" s="1"/>
+      <c r="Z2" s="4"/>
       <c r="AA2" s="5" t="s">
         <v>6</v>
       </c>
@@ -8902,27 +8917,27 @@
     <col min="3" max="3" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="27" max="27" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="28" max="28" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="29" max="29" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -8935,33 +8950,33 @@
         <v>0</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="2"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="1"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="2"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="1"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="4"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="1"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="4"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="1"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="4"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="3"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
@@ -8971,35 +8986,35 @@
         <v>1</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="5"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2" s="1"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="O2" s="6"/>
-      <c r="P2" s="1"/>
+      <c r="P2" s="4"/>
       <c r="Q2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="U2" s="1"/>
+      <c r="U2" s="4"/>
       <c r="V2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
-      <c r="Z2" s="1"/>
+      <c r="Z2" s="4"/>
       <c r="AA2" s="5" t="s">
         <v>6</v>
       </c>
